--- a/csv/model/DCC/formula_DCC_QC.xlsx
+++ b/csv/model/DCC/formula_DCC_QC.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32175" yWindow="990" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M235" t="n">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M237" t="n">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18797,7 +18797,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -19020,7 +19020,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20097,7 +20097,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20319,7 +20319,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -20717,7 +20717,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -20807,7 +20807,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -23568,7 +23568,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -23871,7 +23871,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -23956,7 +23956,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24047,7 +24047,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24259,7 +24259,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24435,7 +24435,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -24647,7 +24647,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -24823,7 +24823,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -24950,7 +24950,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25035,7 +25035,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25423,7 +25423,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -25599,7 +25599,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -25896,7 +25896,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26284,7 +26284,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26375,7 +26375,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -26587,7 +26587,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -26975,7 +26975,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -27278,7 +27278,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -27927,7 +27927,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -28442,7 +28442,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28527,7 +28527,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -28915,7 +28915,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -29176,7 +29176,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -29388,7 +29388,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">

--- a/csv/model/DCC/formula_DCC_QC.xlsx
+++ b/csv/model/DCC/formula_DCC_QC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\dev\cims-models\csv\model\DCC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\test\cims-models\csv\model\DCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1CFA07B-9543-44E7-A87F-5B236FD1D921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5823953A-E545-43DE-A647-359E9D8EE5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94BE17A0-C549-42CB-8BF4-4AF6AFC0B563}"/>
+    <workbookView xWindow="32505" yWindow="2025" windowWidth="38700" windowHeight="15285" xr2:uid="{AED25613-A22D-4B87-BBFE-3855024EFC13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -985,16 +985,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB8F946-9E65-46F9-BD4D-36E4CE7B0A29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6D39FE-447C-496F-B975-AB5014039B40}">
   <dimension ref="A1:X488"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>17.009699999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>6840</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1838,50 +1838,50 @@
         <v>54</v>
       </c>
       <c r="M16">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="V16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="W16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1976,50 +1976,50 @@
         <v>54</v>
       </c>
       <c r="M18">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -3046,50 +3046,50 @@
         <v>54</v>
       </c>
       <c r="M36">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="V36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="W36">
         <f t="shared" ca="1" si="4"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -3184,50 +3184,50 @@
         <v>54</v>
       </c>
       <c r="M38">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W38">
         <f t="shared" ca="1" si="4"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>67</v>
       </c>
@@ -3952,50 +3952,50 @@
         <v>54</v>
       </c>
       <c r="M51">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="V51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="W51">
         <f t="shared" ca="1" si="7"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>67</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>67</v>
       </c>
@@ -4090,50 +4090,50 @@
         <v>54</v>
       </c>
       <c r="M53">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>67</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>67</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>67</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>67</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>73</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>73</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>73</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>75</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>75</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>75</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>75</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>79</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>79</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>79</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>79</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>81</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>81</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>81</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>7668000</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>88</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>88</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>88</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>88</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>88</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>88</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>88</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>88</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>88</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>88</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>88</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>88</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>88</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>88</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>88</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>88</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>88</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>88</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>88</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>88</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>88</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>88</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>88</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>88</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>88</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>88</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>88</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>88</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>88</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>88</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>88</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>88</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>88</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>88</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>88</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>88</v>
       </c>
@@ -9023,7 +9023,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>88</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>88</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>88</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>88</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>88</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>88</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>88</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>88</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>88</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>105</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>105</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>105</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>105</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>200000000</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>105</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>109</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>109</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>109</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>109</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>109</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>110</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>110</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>110</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>110</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>110</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>112</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>112</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>112</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>112</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>112</v>
       </c>
@@ -10823,7 +10823,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>112</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>112</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>112</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>112</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>112</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>120</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>120</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>120</v>
       </c>
@@ -11289,7 +11289,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>120</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>120</v>
       </c>
@@ -11427,7 +11427,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>120</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>120</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>120</v>
       </c>
@@ -11591,7 +11591,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>120</v>
       </c>
@@ -11660,7 +11660,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>120</v>
       </c>
@@ -11729,7 +11729,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>122</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>122</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>122</v>
       </c>
@@ -11893,7 +11893,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>122</v>
       </c>
@@ -11963,7 +11963,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>122</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>123</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>123</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>123</v>
       </c>
@@ -12196,7 +12196,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>123</v>
       </c>
@@ -12265,7 +12265,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>123</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>128</v>
       </c>
@@ -12360,7 +12360,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>128</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>128</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>128</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>128</v>
       </c>
@@ -12637,7 +12637,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>129</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>129</v>
       </c>
@@ -12689,7 +12689,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>135</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>135</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>136</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>136</v>
       </c>
@@ -12793,7 +12793,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>137</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>137</v>
       </c>
@@ -12845,7 +12845,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>137</v>
       </c>
@@ -12871,7 +12871,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>139</v>
       </c>
@@ -12897,7 +12897,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>139</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>139</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>140</v>
       </c>
@@ -12975,7 +12975,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>140</v>
       </c>
@@ -13001,7 +13001,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>140</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>141</v>
       </c>
@@ -13053,7 +13053,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>141</v>
       </c>
@@ -13079,7 +13079,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>142</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>142</v>
       </c>
@@ -13131,7 +13131,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>143</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>143</v>
       </c>
@@ -13183,7 +13183,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>144</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>144</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>145</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>145</v>
       </c>
@@ -13287,7 +13287,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>146</v>
       </c>
@@ -13313,7 +13313,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>146</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>129</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>129</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>135</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>135</v>
       </c>
@@ -13563,7 +13563,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>136</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>136</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>137</v>
       </c>
@@ -13731,7 +13731,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>137</v>
       </c>
@@ -13787,7 +13787,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>137</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>139</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>139</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>139</v>
       </c>
@@ -14011,7 +14011,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>140</v>
       </c>
@@ -14067,7 +14067,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>140</v>
       </c>
@@ -14123,7 +14123,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>140</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>141</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>141</v>
       </c>
@@ -14291,7 +14291,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>142</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>142</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>143</v>
       </c>
@@ -14459,7 +14459,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>143</v>
       </c>
@@ -14515,7 +14515,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>144</v>
       </c>
@@ -14571,7 +14571,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>144</v>
       </c>
@@ -14627,7 +14627,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>145</v>
       </c>
@@ -14683,7 +14683,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>145</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>146</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>146</v>
       </c>
@@ -14851,7 +14851,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>129</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>129</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>135</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>135</v>
       </c>
@@ -15075,7 +15075,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>136</v>
       </c>
@@ -15131,7 +15131,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>136</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>137</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>137</v>
       </c>
@@ -15299,7 +15299,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>137</v>
       </c>
@@ -15355,7 +15355,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>139</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>139</v>
       </c>
@@ -15467,7 +15467,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>139</v>
       </c>
@@ -15523,7 +15523,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>140</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>140</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>140</v>
       </c>
@@ -15691,7 +15691,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>141</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>141</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>142</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>142</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>143</v>
       </c>
@@ -15971,7 +15971,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>143</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>144</v>
       </c>
@@ -16083,7 +16083,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>144</v>
       </c>
@@ -16139,7 +16139,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>145</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>145</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>146</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>146</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>129</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>129</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>135</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>135</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>136</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>136</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>137</v>
       </c>
@@ -16755,7 +16755,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>137</v>
       </c>
@@ -16811,7 +16811,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>137</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>139</v>
       </c>
@@ -16923,7 +16923,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>139</v>
       </c>
@@ -16979,7 +16979,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>139</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>140</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>140</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>140</v>
       </c>
@@ -17203,7 +17203,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>141</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>141</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>142</v>
       </c>
@@ -17371,7 +17371,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>142</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>143</v>
       </c>
@@ -17483,7 +17483,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>143</v>
       </c>
@@ -17539,7 +17539,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>144</v>
       </c>
@@ -17595,7 +17595,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>144</v>
       </c>
@@ -17651,7 +17651,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>145</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>145</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>146</v>
       </c>
@@ -17819,7 +17819,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>146</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>129</v>
       </c>
@@ -17931,7 +17931,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>129</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>135</v>
       </c>
@@ -18043,7 +18043,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>135</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>136</v>
       </c>
@@ -18155,7 +18155,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>136</v>
       </c>
@@ -18211,7 +18211,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>137</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>137</v>
       </c>
@@ -18323,7 +18323,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>137</v>
       </c>
@@ -18379,7 +18379,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>139</v>
       </c>
@@ -18435,7 +18435,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>139</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>139</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>140</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>140</v>
       </c>
@@ -18659,7 +18659,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>140</v>
       </c>
@@ -18715,7 +18715,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>141</v>
       </c>
@@ -18771,7 +18771,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>141</v>
       </c>
@@ -18827,7 +18827,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>142</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>142</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="321" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>143</v>
       </c>
@@ -18995,7 +18995,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="322" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>143</v>
       </c>
@@ -19051,7 +19051,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="323" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>144</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="324" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>144</v>
       </c>
@@ -19163,7 +19163,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>145</v>
       </c>
@@ -19219,7 +19219,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>145</v>
       </c>
@@ -19275,7 +19275,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="327" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>146</v>
       </c>
@@ -19331,7 +19331,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="328" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>146</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="329" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>27</v>
       </c>
@@ -19413,7 +19413,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="330" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>27</v>
       </c>
@@ -19485,7 +19485,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="331" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>27</v>
       </c>
@@ -19557,7 +19557,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="332" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>27</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="333" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>27</v>
       </c>
@@ -19701,7 +19701,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="334" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>27</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="335" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>27</v>
       </c>
@@ -19802,7 +19802,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="336" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>27</v>
       </c>
@@ -19874,7 +19874,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="337" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>27</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="338" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>27</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="339" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>27</v>
       </c>
@@ -20045,7 +20045,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="340" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>27</v>
       </c>
@@ -20117,7 +20117,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="341" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>27</v>
       </c>
@@ -20189,7 +20189,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="342" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>27</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="343" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>27</v>
       </c>
@@ -20334,7 +20334,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="344" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>29</v>
       </c>
@@ -20360,7 +20360,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="345" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>29</v>
       </c>
@@ -20429,7 +20429,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="346" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>29</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="347" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>29</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="348" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>29</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="349" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>29</v>
       </c>
@@ -20666,7 +20666,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="350" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>29</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="351" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>29</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>29</v>
       </c>
@@ -20877,7 +20877,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="353" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>29</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="354" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>21</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="355" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>21</v>
       </c>
@@ -21047,7 +21047,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="356" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>21</v>
       </c>
@@ -21119,7 +21119,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="357" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>21</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="358" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>21</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="359" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>21</v>
       </c>
@@ -21290,7 +21290,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="360" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>21</v>
       </c>
@@ -21362,7 +21362,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="361" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>21</v>
       </c>
@@ -21434,7 +21434,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="362" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>21</v>
       </c>
@@ -21507,7 +21507,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="363" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>21</v>
       </c>
@@ -21579,7 +21579,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="364" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>21</v>
       </c>
@@ -21605,7 +21605,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="365" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>21</v>
       </c>
@@ -21677,7 +21677,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="366" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>21</v>
       </c>
@@ -21749,7 +21749,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="367" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>21</v>
       </c>
@@ -21822,7 +21822,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="368" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>21</v>
       </c>
@@ -21894,7 +21894,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="369" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>21</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="370" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>21</v>
       </c>
@@ -21992,7 +21992,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="371" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>21</v>
       </c>
@@ -22064,7 +22064,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="372" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>21</v>
       </c>
@@ -22137,7 +22137,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="373" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>21</v>
       </c>
@@ -22209,7 +22209,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="374" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>165</v>
       </c>
@@ -22235,7 +22235,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="375" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>165</v>
       </c>
@@ -22304,7 +22304,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="376" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>165</v>
       </c>
@@ -22376,7 +22376,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="377" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>165</v>
       </c>
@@ -22449,7 +22449,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="378" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>165</v>
       </c>
@@ -22521,7 +22521,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="379" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>165</v>
       </c>
@@ -22547,7 +22547,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="380" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>165</v>
       </c>
@@ -22616,7 +22616,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="381" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>165</v>
       </c>
@@ -22688,7 +22688,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="382" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>165</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="383" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>165</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="384" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>165</v>
       </c>
@@ -22859,7 +22859,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="385" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>165</v>
       </c>
@@ -22928,7 +22928,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="386" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>165</v>
       </c>
@@ -23000,7 +23000,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="387" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>165</v>
       </c>
@@ -23073,7 +23073,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="388" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>165</v>
       </c>
@@ -23145,7 +23145,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="389" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>165</v>
       </c>
@@ -23171,7 +23171,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="390" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>165</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="391" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>165</v>
       </c>
@@ -23312,7 +23312,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="392" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>165</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="393" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>165</v>
       </c>
@@ -23457,7 +23457,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="394" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>165</v>
       </c>
@@ -23483,7 +23483,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="395" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>165</v>
       </c>
@@ -23552,7 +23552,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="396" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>165</v>
       </c>
@@ -23624,7 +23624,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="397" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>165</v>
       </c>
@@ -23697,7 +23697,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="398" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>165</v>
       </c>
@@ -23769,7 +23769,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="399" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>31</v>
       </c>
@@ -23795,7 +23795,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="400" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>31</v>
       </c>
@@ -23864,7 +23864,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="401" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>31</v>
       </c>
@@ -23933,7 +23933,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="402" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>31</v>
       </c>
@@ -24006,7 +24006,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="403" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>31</v>
       </c>
@@ -24075,7 +24075,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="404" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>31</v>
       </c>
@@ -24101,7 +24101,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="405" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>31</v>
       </c>
@@ -24170,7 +24170,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="406" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>31</v>
       </c>
@@ -24239,7 +24239,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="407" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>31</v>
       </c>
@@ -24312,7 +24312,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="408" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>31</v>
       </c>
@@ -24381,7 +24381,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="409" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>31</v>
       </c>
@@ -24407,7 +24407,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="410" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>31</v>
       </c>
@@ -24476,7 +24476,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="411" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>31</v>
       </c>
@@ -24545,7 +24545,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="412" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>31</v>
       </c>
@@ -24618,7 +24618,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="413" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>31</v>
       </c>
@@ -24687,7 +24687,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="414" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>31</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="415" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>31</v>
       </c>
@@ -24782,7 +24782,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="416" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>31</v>
       </c>
@@ -24851,7 +24851,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>31</v>
       </c>
@@ -24924,7 +24924,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="418" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>31</v>
       </c>
@@ -24993,7 +24993,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="419" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>31</v>
       </c>
@@ -25019,7 +25019,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="420" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>31</v>
       </c>
@@ -25088,7 +25088,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="421" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>31</v>
       </c>
@@ -25157,7 +25157,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>31</v>
       </c>
@@ -25230,7 +25230,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="423" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>31</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="424" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>31</v>
       </c>
@@ -25325,7 +25325,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="425" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>31</v>
       </c>
@@ -25394,7 +25394,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="426" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>31</v>
       </c>
@@ -25463,7 +25463,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="427" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>31</v>
       </c>
@@ -25536,7 +25536,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="428" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>31</v>
       </c>
@@ -25605,7 +25605,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="429" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>35</v>
       </c>
@@ -25631,7 +25631,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="430" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>35</v>
       </c>
@@ -25700,7 +25700,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="431" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>35</v>
       </c>
@@ -25769,7 +25769,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="432" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>35</v>
       </c>
@@ -25842,7 +25842,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="433" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>35</v>
       </c>
@@ -25911,7 +25911,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="434" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>35</v>
       </c>
@@ -25937,7 +25937,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="435" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>35</v>
       </c>
@@ -26006,7 +26006,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="436" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>35</v>
       </c>
@@ -26075,7 +26075,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="437" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>35</v>
       </c>
@@ -26148,7 +26148,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="438" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>35</v>
       </c>
@@ -26217,7 +26217,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="439" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>35</v>
       </c>
@@ -26243,7 +26243,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="440" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>35</v>
       </c>
@@ -26312,7 +26312,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="441" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>35</v>
       </c>
@@ -26381,7 +26381,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="442" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>35</v>
       </c>
@@ -26454,7 +26454,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="443" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>35</v>
       </c>
@@ -26523,7 +26523,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="444" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>35</v>
       </c>
@@ -26549,7 +26549,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="445" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>35</v>
       </c>
@@ -26618,7 +26618,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="446" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>35</v>
       </c>
@@ -26687,7 +26687,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="447" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>35</v>
       </c>
@@ -26760,7 +26760,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="448" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>35</v>
       </c>
@@ -26829,7 +26829,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="449" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>35</v>
       </c>
@@ -26855,7 +26855,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="450" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>35</v>
       </c>
@@ -26924,7 +26924,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="451" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>35</v>
       </c>
@@ -26993,7 +26993,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="452" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>35</v>
       </c>
@@ -27066,7 +27066,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="453" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>35</v>
       </c>
@@ -27135,7 +27135,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="454" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>35</v>
       </c>
@@ -27161,7 +27161,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="455" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>35</v>
       </c>
@@ -27230,7 +27230,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="456" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>35</v>
       </c>
@@ -27299,7 +27299,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="457" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>35</v>
       </c>
@@ -27372,7 +27372,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="458" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>35</v>
       </c>
@@ -27441,7 +27441,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="459" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>37</v>
       </c>
@@ -27467,7 +27467,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="460" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>37</v>
       </c>
@@ -27536,7 +27536,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="461" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>37</v>
       </c>
@@ -27605,7 +27605,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="462" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>37</v>
       </c>
@@ -27678,7 +27678,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="463" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>37</v>
       </c>
@@ -27747,7 +27747,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="464" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>37</v>
       </c>
@@ -27773,7 +27773,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="465" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>37</v>
       </c>
@@ -27842,7 +27842,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="466" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>37</v>
       </c>
@@ -27911,7 +27911,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>37</v>
       </c>
@@ -27984,7 +27984,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="468" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>37</v>
       </c>
@@ -28053,7 +28053,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="469" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>37</v>
       </c>
@@ -28079,7 +28079,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="470" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>37</v>
       </c>
@@ -28148,7 +28148,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="471" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>37</v>
       </c>
@@ -28217,7 +28217,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="472" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>37</v>
       </c>
@@ -28290,7 +28290,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="473" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>37</v>
       </c>
@@ -28359,7 +28359,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="474" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>40</v>
       </c>
@@ -28385,7 +28385,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="475" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>40</v>
       </c>
@@ -28454,7 +28454,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="476" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>40</v>
       </c>
@@ -28523,7 +28523,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="477" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>40</v>
       </c>
@@ -28596,7 +28596,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="478" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>40</v>
       </c>
@@ -28665,7 +28665,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="479" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>40</v>
       </c>
@@ -28691,7 +28691,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="480" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>40</v>
       </c>
@@ -28760,7 +28760,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="481" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>40</v>
       </c>
@@ -28829,7 +28829,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="482" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>40</v>
       </c>
@@ -28902,7 +28902,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="483" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>40</v>
       </c>
@@ -28971,7 +28971,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="484" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>189</v>
       </c>
@@ -28997,7 +28997,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="485" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>189</v>
       </c>
@@ -29066,7 +29066,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="486" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>189</v>
       </c>
@@ -29135,7 +29135,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="487" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>189</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>92227251.175370395</v>
       </c>
     </row>
-    <row r="488" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>189</v>
       </c>
